--- a/sheets/대금율보/검수/죽지사(竹枝詞).xlsx
+++ b/sheets/대금율보/검수/죽지사(竹枝詞).xlsx
@@ -8142,32 +8142,32 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="13.46" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="13.46" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="13.46" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="13.46" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="13.46" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="13.46" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="13.46" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="13.46" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="18" max="18" width="13.46" customWidth="1"/>
     <col min="19" max="19" width="6" customWidth="1"/>
-    <col min="20" max="20" width="9" customWidth="1"/>
+    <col min="20" max="20" width="13.46" customWidth="1"/>
     <col min="21" max="21" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="93.02" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -8194,7 +8194,7 @@
       <c r="T2" s="20"/>
       <c r="U2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="277.43" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -8310,7 +8310,7 @@
       </c>
       <c r="U3" s="22"/>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="277.43" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -8414,7 +8414,7 @@
       </c>
       <c r="U4" s="22"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="277.43" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21"/>
       <c r="C5" s="22"/>
@@ -8513,7 +8513,7 @@
       </c>
       <c r="U5" s="22"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="277.43" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -8624,7 +8624,7 @@
       </c>
       <c r="U6" s="22"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="277.43" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -8716,7 +8716,7 @@
       </c>
       <c r="U7" s="22"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="277.43" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -8808,10 +8808,10 @@
       </c>
       <c r="U8" s="22"/>
     </row>
-    <row r="9">
+    <row r="9" ht="6.0" customHeight="true">
       <c r="A9" s="0"/>
     </row>
-    <row r="10" ht="60" customHeight="1">
+    <row r="10" ht="93.02" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="20" t="inlineStr">
         <is>
@@ -8838,7 +8838,7 @@
       <c r="T10" s="20"/>
       <c r="U10" s="20"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="277.43" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -8959,7 +8959,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="277.43" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -9055,7 +9055,7 @@
       </c>
       <c r="U12" s="22"/>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="277.43" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -9162,7 +9162,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="277.43" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -9269,7 +9269,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="277.43" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="21" t="inlineStr">
         <is>
@@ -9338,7 +9338,7 @@
       </c>
       <c r="U15" s="22"/>
     </row>
-    <row r="16" ht="56" customHeight="1">
+    <row r="16" ht="277.43" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="21" t="inlineStr">
         <is>
@@ -9434,10 +9434,10 @@
         </is>
       </c>
     </row>
-    <row r="17">
+    <row r="17" ht="6.0" customHeight="true">
       <c r="A17" s="0"/>
     </row>
-    <row r="18" ht="60" customHeight="1">
+    <row r="18" ht="93.02" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="20" t="inlineStr">
         <is>
@@ -9464,7 +9464,7 @@
       <c r="T18" s="20"/>
       <c r="U18" s="20"/>
     </row>
-    <row r="19" ht="56" customHeight="1">
+    <row r="19" ht="277.43" customHeight="true">
       <c r="A19" s="0"/>
       <c r="B19" s="21" t="inlineStr">
         <is>
@@ -9582,7 +9582,7 @@
       </c>
       <c r="U19" s="22"/>
     </row>
-    <row r="20" ht="56" customHeight="1">
+    <row r="20" ht="277.43" customHeight="true">
       <c r="A20" s="0"/>
       <c r="B20" s="21" t="inlineStr">
         <is>
@@ -9679,7 +9679,7 @@
       </c>
       <c r="U20" s="22"/>
     </row>
-    <row r="21" ht="56" customHeight="1">
+    <row r="21" ht="277.43" customHeight="true">
       <c r="A21" s="0"/>
       <c r="B21" s="21" t="inlineStr">
         <is>
@@ -9784,7 +9784,7 @@
       </c>
       <c r="U21" s="22"/>
     </row>
-    <row r="22" ht="56" customHeight="1">
+    <row r="22" ht="277.43" customHeight="true">
       <c r="A22" s="0"/>
       <c r="B22" s="21" t="inlineStr">
         <is>
@@ -9894,7 +9894,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="56" customHeight="1">
+    <row r="23" ht="277.43" customHeight="true">
       <c r="A23" s="0"/>
       <c r="B23" s="21"/>
       <c r="C23" s="22"/>
@@ -9972,7 +9972,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="56" customHeight="1">
+    <row r="24" ht="277.43" customHeight="true">
       <c r="A24" s="0"/>
       <c r="B24" s="21" t="inlineStr">
         <is>
@@ -10064,10 +10064,10 @@
         </is>
       </c>
     </row>
-    <row r="25">
+    <row r="25" ht="6.0" customHeight="true">
       <c r="A25" s="0"/>
     </row>
-    <row r="26" ht="60" customHeight="1">
+    <row r="26" ht="93.02" customHeight="true">
       <c r="A26" s="0"/>
       <c r="B26" s="20" t="inlineStr">
         <is>
@@ -10094,7 +10094,7 @@
       <c r="T26" s="20"/>
       <c r="U26" s="20"/>
     </row>
-    <row r="27" ht="56" customHeight="1">
+    <row r="27" ht="277.43" customHeight="true">
       <c r="A27" s="0"/>
       <c r="B27" s="21"/>
       <c r="C27" s="22"/>
@@ -10168,7 +10168,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="56" customHeight="1">
+    <row r="28" ht="277.43" customHeight="true">
       <c r="A28" s="0"/>
       <c r="B28" s="21"/>
       <c r="C28" s="22"/>
@@ -10226,7 +10226,7 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="56" customHeight="1">
+    <row r="29" ht="277.43" customHeight="true">
       <c r="A29" s="0"/>
       <c r="B29" s="21"/>
       <c r="C29" s="22"/>
@@ -10287,7 +10287,7 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="56" customHeight="1">
+    <row r="30" ht="277.43" customHeight="true">
       <c r="A30" s="0"/>
       <c r="B30" s="21"/>
       <c r="C30" s="22"/>
@@ -10356,7 +10356,7 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="56" customHeight="1">
+    <row r="31" ht="277.43" customHeight="true">
       <c r="A31" s="0"/>
       <c r="B31" s="21"/>
       <c r="C31" s="22"/>
@@ -10416,7 +10416,7 @@
       </c>
       <c r="U31" s="22"/>
     </row>
-    <row r="32" ht="56" customHeight="1">
+    <row r="32" ht="277.43" customHeight="true">
       <c r="A32" s="0"/>
       <c r="B32" s="21"/>
       <c r="C32" s="22"/>
@@ -10481,7 +10481,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="61"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="43"/>
   <rowBreaks count="3" manualBreakCount="3">
     <brk id="8" max="16383" man="1"/>
     <brk id="16" max="16383" man="1"/>
